--- a/xuat-kho/samples/Phieu-xuat-kho-mau.xlsx
+++ b/xuat-kho/samples/Phieu-xuat-kho-mau.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -151,6 +151,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,13 +624,13 @@
       <c r="A12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Thịt lợn luộc</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -641,19 +647,19 @@
       <c r="H12" s="8" t="n">
         <v>516000</v>
       </c>
-      <c r="I12" s="7" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
     </row>
     <row r="13" ht="23.1" customHeight="1">
       <c r="A13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Lạc rang</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -670,19 +676,19 @@
       <c r="H13" s="8" t="n">
         <v>77000</v>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
     </row>
     <row r="14" ht="23.1" customHeight="1">
       <c r="A14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Rau muống</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>tập</t>
         </is>
@@ -699,7 +705,7 @@
       <c r="H14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>Rau Nhà trường có</t>
         </is>
@@ -945,7 +951,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1146,13 +1152,13 @@
       <c r="A12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Thịt lợn luộc</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1169,19 +1175,19 @@
       <c r="H12" s="8" t="n">
         <v>336000</v>
       </c>
-      <c r="I12" s="7" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
     </row>
     <row r="13" ht="23.1" customHeight="1">
       <c r="A13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Lạc rang</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1198,19 +1204,19 @@
       <c r="H13" s="8" t="n">
         <v>56000</v>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
     </row>
     <row r="14" ht="23.1" customHeight="1">
       <c r="A14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Rau muống</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1227,7 +1233,7 @@
       <c r="H14" s="8" t="n">
         <v>40000</v>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
+      <c r="I14" s="17" t="inlineStr"/>
     </row>
     <row r="15" ht="23.1" customHeight="1">
       <c r="A15" s="9" t="n"/>
@@ -1469,7 +1475,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1670,13 +1676,13 @@
       <c r="A12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Thịt lợn luộc</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1693,19 +1699,19 @@
       <c r="H12" s="8" t="n">
         <v>420000</v>
       </c>
-      <c r="I12" s="7" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
     </row>
     <row r="13" ht="23.1" customHeight="1">
       <c r="A13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Lạc rang</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1722,19 +1728,19 @@
       <c r="H13" s="8" t="n">
         <v>70000</v>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
     </row>
     <row r="14" ht="23.1" customHeight="1">
       <c r="A14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Rau muống</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>tập</t>
         </is>
@@ -1751,7 +1757,7 @@
       <c r="H14" s="8" t="n">
         <v>54000</v>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
+      <c r="I14" s="17" t="inlineStr"/>
     </row>
     <row r="15" ht="23.1" customHeight="1">
       <c r="A15" s="9" t="n"/>
@@ -1993,6 +1999,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>